--- a/report_6.xlsx
+++ b/report_6.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q106"/>
+  <dimension ref="A1:Q105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6289,37 +6289,37 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>D204118</t>
+          <t>D204780</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>C2779</t>
+          <t>C2790</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Clinic_979</t>
+          <t>Clinic_990</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Oncology</t>
+          <t>Pathology</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>MDX-100</t>
+          <t>UltiScan V2</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>S-671897</t>
+          <t>S-393381</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
@@ -6329,11 +6329,9 @@
         </is>
       </c>
       <c r="J92" s="1" t="n">
-        <v>46131</v>
-      </c>
-      <c r="K92" s="1" t="n">
-        <v>45373</v>
-      </c>
+        <v>46721</v>
+      </c>
+      <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="n">
         <v>0</v>
@@ -6342,7 +6340,7 @@
         <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>97.19</v>
+        <v>98.41</v>
       </c>
       <c r="P92" t="inlineStr"/>
       <c r="Q92" t="b">
@@ -6352,37 +6350,37 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>D204780</t>
+          <t>D203443</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>C2790</t>
+          <t>C2720</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Clinic_990</t>
+          <t>Clinic_920</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Pathology</t>
+          <t>Emergency</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>UltiScan V2</t>
+          <t>NeoScan X</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>S-393381</t>
+          <t>S-389700</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
@@ -6392,20 +6390,24 @@
         </is>
       </c>
       <c r="J93" s="1" t="n">
-        <v>46721</v>
+        <v>47018</v>
       </c>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O93" t="n">
-        <v>98.41</v>
-      </c>
-      <c r="P93" t="inlineStr"/>
+        <v>99.59999999999999</v>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>overheat</t>
+        </is>
+      </c>
       <c r="Q93" t="b">
         <v>1</v>
       </c>
@@ -6413,64 +6415,64 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>D203443</t>
+          <t>D201187</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>C2720</t>
+          <t>C2795</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Clinic_920</t>
+          <t>Clinic_995</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Madrid</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Emergency</t>
+          <t>Cardiology</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>NeoScan X</t>
+          <t>UltiScan V2</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>S-389700</t>
+          <t>S-379016</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>planned_installation</t>
         </is>
       </c>
       <c r="J94" s="1" t="n">
-        <v>47018</v>
-      </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
+        <v>46592</v>
+      </c>
+      <c r="K94" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="L94" s="1" t="n">
+        <v>46227</v>
+      </c>
       <c r="M94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>overheat</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P94" t="inlineStr"/>
       <c r="Q94" t="b">
         <v>1</v>
       </c>
@@ -6478,64 +6480,66 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>D201187</t>
+          <t>D206208</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>C2795</t>
+          <t>C2158</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Clinic_995</t>
+          <t>Clinic_358</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>Yekaterinburg</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Cardiology</t>
+          <t>Radiology</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>UltiScan V2</t>
+          <t>UltraDiag-3</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>S-379016</t>
+          <t>S-258074</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
-          <t>planned_installation</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="J95" s="1" t="n">
-        <v>46592</v>
+        <v>47035</v>
       </c>
       <c r="K95" s="1" t="n">
-        <v>46227</v>
-      </c>
-      <c r="L95" s="1" t="n">
-        <v>46227</v>
-      </c>
+        <v>46028</v>
+      </c>
+      <c r="L95" t="inlineStr"/>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O95" t="n">
-        <v>0</v>
-      </c>
-      <c r="P95" t="inlineStr"/>
+        <v>97.90000000000001</v>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>network disconnect; calibration drift</t>
+        </is>
+      </c>
       <c r="Q95" t="b">
         <v>1</v>
       </c>
@@ -6543,22 +6547,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>D206208</t>
+          <t>D200921</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>C2158</t>
+          <t>C2634</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Clinic_358</t>
+          <t>Clinic_834</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Yekaterinburg</t>
+          <t>Novosibirsk</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6568,41 +6572,37 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>UltraDiag-3</t>
+          <t>SafeScan Pro</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>S-258074</t>
+          <t>S-516939</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>maintenance_scheduled</t>
         </is>
       </c>
       <c r="J96" s="1" t="n">
-        <v>47035</v>
+        <v>46673</v>
       </c>
       <c r="K96" s="1" t="n">
-        <v>46028</v>
+        <v>45696</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
-        <v>97.90000000000001</v>
-      </c>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>network disconnect; calibration drift</t>
-        </is>
-      </c>
+        <v>93.84</v>
+      </c>
+      <c r="P96" t="inlineStr"/>
       <c r="Q96" t="b">
         <v>1</v>
       </c>
@@ -6610,52 +6610,52 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>D200921</t>
+          <t>D202216</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>C2634</t>
+          <t>C2136</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Clinic_834</t>
+          <t>Clinic_336</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Novosibirsk</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Radiology</t>
+          <t>General Diagnostics</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>SafeScan Pro</t>
+          <t>UltiScan V2</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>S-516939</t>
+          <t>S-927233</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
-          <t>maintenance_scheduled</t>
+          <t>planned_installation</t>
         </is>
       </c>
       <c r="J97" s="1" t="n">
-        <v>46673</v>
-      </c>
-      <c r="K97" s="1" t="n">
-        <v>45696</v>
-      </c>
-      <c r="L97" t="inlineStr"/>
+        <v>47253</v>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" s="1" t="n">
+        <v>46158</v>
+      </c>
       <c r="M97" t="n">
         <v>0</v>
       </c>
@@ -6663,7 +6663,7 @@
         <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>93.84</v>
+        <v>0</v>
       </c>
       <c r="P97" t="inlineStr"/>
       <c r="Q97" t="b">
@@ -6673,37 +6673,37 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>D202216</t>
+          <t>D205493</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>C2136</t>
+          <t>C2279</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Clinic_336</t>
+          <t>Clinic_479</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>General Diagnostics</t>
+          <t>Cardiology</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>UltiScan V2</t>
+          <t>SafeScan Pro</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>S-927233</t>
+          <t>S-845741</t>
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
@@ -6713,12 +6713,12 @@
         </is>
       </c>
       <c r="J98" s="1" t="n">
-        <v>47253</v>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" s="1" t="n">
-        <v>46158</v>
-      </c>
+        <v>47419</v>
+      </c>
+      <c r="K98" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="L98" t="inlineStr"/>
       <c r="M98" t="n">
         <v>0</v>
       </c>
@@ -6736,22 +6736,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>D205493</t>
+          <t>D200375</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>C2279</t>
+          <t>C2227</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Clinic_479</t>
+          <t>Clinic_427</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Beijing</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6761,25 +6761,25 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>SafeScan Pro</t>
+          <t>NeoScan X</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>S-845741</t>
+          <t>S-652103</t>
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
-          <t>planned_installation</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="J99" s="1" t="n">
-        <v>47419</v>
+        <v>46455</v>
       </c>
       <c r="K99" s="1" t="n">
-        <v>46324</v>
+        <v>45325</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="n">
@@ -6789,7 +6789,7 @@
         <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
+        <v>97.86</v>
       </c>
       <c r="P99" t="inlineStr"/>
       <c r="Q99" t="b">
@@ -6799,22 +6799,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>D200375</t>
+          <t>D209933</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>C2227</t>
+          <t>C2338</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Clinic_427</t>
+          <t>Clinic_538</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6824,27 +6824,31 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>NeoScan X</t>
+          <t>SafeScan Pro</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>S-652103</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+          <t>S-878827</t>
+        </is>
+      </c>
+      <c r="H100" s="1" t="n">
+        <v>45601</v>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
           <t>operational</t>
         </is>
       </c>
       <c r="J100" s="1" t="n">
-        <v>46455</v>
+        <v>46518</v>
       </c>
       <c r="K100" s="1" t="n">
-        <v>45325</v>
-      </c>
-      <c r="L100" t="inlineStr"/>
+        <v>45765</v>
+      </c>
+      <c r="L100" s="1" t="n">
+        <v>45467</v>
+      </c>
       <c r="M100" t="n">
         <v>0</v>
       </c>
@@ -6852,7 +6856,7 @@
         <v>0</v>
       </c>
       <c r="O100" t="n">
-        <v>97.86</v>
+        <v>96.20999999999999</v>
       </c>
       <c r="P100" t="inlineStr"/>
       <c r="Q100" t="b">
@@ -6862,41 +6866,41 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>D209933</t>
+          <t>D207230</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>C2338</t>
+          <t>C2348</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Clinic_538</t>
+          <t>Clinic_548</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Cardiology</t>
+          <t>Emergency</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>SafeScan Pro</t>
+          <t>UltiScan V2</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>S-878827</t>
+          <t>S-551886</t>
         </is>
       </c>
       <c r="H101" s="1" t="n">
-        <v>45601</v>
+        <v>45118</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -6904,14 +6908,10 @@
         </is>
       </c>
       <c r="J101" s="1" t="n">
-        <v>46518</v>
-      </c>
-      <c r="K101" s="1" t="n">
-        <v>45765</v>
-      </c>
-      <c r="L101" s="1" t="n">
-        <v>45467</v>
-      </c>
+        <v>46332</v>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
       <c r="M101" t="n">
         <v>0</v>
       </c>
@@ -6919,7 +6919,7 @@
         <v>0</v>
       </c>
       <c r="O101" t="n">
-        <v>96.20999999999999</v>
+        <v>96.88</v>
       </c>
       <c r="P101" t="inlineStr"/>
       <c r="Q101" t="b">
@@ -6929,41 +6929,41 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>D207230</t>
+          <t>D203783</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>C2348</t>
+          <t>C2206</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Clinic_548</t>
+          <t>Clinic_406</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Novosibirsk</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Emergency</t>
+          <t>Oncology</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>UltiScan V2</t>
+          <t>NeoScan X</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>S-551886</t>
+          <t>S-917026</t>
         </is>
       </c>
       <c r="H102" s="1" t="n">
-        <v>45118</v>
+        <v>45661</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -6971,20 +6971,26 @@
         </is>
       </c>
       <c r="J102" s="1" t="n">
-        <v>46332</v>
+        <v>46478</v>
       </c>
       <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
+      <c r="L102" s="1" t="n">
+        <v>45777</v>
+      </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O102" t="n">
-        <v>96.88</v>
-      </c>
-      <c r="P102" t="inlineStr"/>
+        <v>98.51000000000001</v>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>power failure</t>
+        </is>
+      </c>
       <c r="Q102" t="b">
         <v>1</v>
       </c>
@@ -6992,27 +6998,27 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>D203783</t>
+          <t>D207508</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>C2206</t>
+          <t>C2746</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Clinic_406</t>
+          <t>Clinic_946</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Novosibirsk</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Oncology</t>
+          <t>General Diagnostics</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -7022,38 +7028,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>S-917026</t>
-        </is>
-      </c>
-      <c r="H103" s="1" t="n">
-        <v>45661</v>
-      </c>
+          <t>S-475645</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
           <t>operational</t>
         </is>
       </c>
       <c r="J103" s="1" t="n">
-        <v>46478</v>
+        <v>46382</v>
       </c>
       <c r="K103" t="inlineStr"/>
       <c r="L103" s="1" t="n">
-        <v>45777</v>
+        <v>45369</v>
       </c>
       <c r="M103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
-        <v>98.51000000000001</v>
-      </c>
-      <c r="P103" t="inlineStr">
-        <is>
-          <t>power failure</t>
-        </is>
-      </c>
+        <v>98.48</v>
+      </c>
+      <c r="P103" t="inlineStr"/>
       <c r="Q103" t="b">
         <v>1</v>
       </c>
@@ -7061,52 +7061,50 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>D207508</t>
+          <t>D204417</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>C2746</t>
+          <t>C2403</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Clinic_946</t>
+          <t>Clinic_603</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>General Diagnostics</t>
+          <t>Pathology</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>NeoScan X</t>
+          <t>UltraDiag-3</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>S-475645</t>
+          <t>S-200957</t>
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>planned_installation</t>
         </is>
       </c>
       <c r="J104" s="1" t="n">
-        <v>46382</v>
+        <v>47388</v>
       </c>
       <c r="K104" t="inlineStr"/>
-      <c r="L104" s="1" t="n">
-        <v>45369</v>
-      </c>
+      <c r="L104" t="inlineStr"/>
       <c r="M104" t="n">
         <v>0</v>
       </c>
@@ -7114,7 +7112,7 @@
         <v>0</v>
       </c>
       <c r="O104" t="n">
-        <v>98.48</v>
+        <v>0</v>
       </c>
       <c r="P104" t="inlineStr"/>
       <c r="Q104" t="b">
@@ -7124,128 +7122,67 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>D204417</t>
+          <t>D208184</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>C2403</t>
+          <t>C2650</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Clinic_603</t>
+          <t>Clinic_850</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Novosibirsk</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Pathology</t>
+          <t>Cardiology</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>UltraDiag-3</t>
+          <t>UltiScan V2</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>S-200957</t>
+          <t>S-704394</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
-          <t>planned_installation</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="J105" s="1" t="n">
-        <v>47388</v>
+        <v>46975</v>
       </c>
       <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
+      <c r="L105" s="1" t="n">
+        <v>45938</v>
+      </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O105" t="n">
-        <v>0</v>
-      </c>
-      <c r="P105" t="inlineStr"/>
+        <v>97.45</v>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>calibration drift</t>
+        </is>
+      </c>
       <c r="Q105" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>D208184</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>C2650</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Clinic_850</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Novosibirsk</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Cardiology</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>UltiScan V2</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>S-704394</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-      <c r="J106" s="1" t="n">
-        <v>46975</v>
-      </c>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" s="1" t="n">
-        <v>45938</v>
-      </c>
-      <c r="M106" t="n">
-        <v>1</v>
-      </c>
-      <c r="N106" t="n">
-        <v>1</v>
-      </c>
-      <c r="O106" t="n">
-        <v>97.45</v>
-      </c>
-      <c r="P106" t="inlineStr">
-        <is>
-          <t>calibration drift</t>
-        </is>
-      </c>
-      <c r="Q106" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8951,7 +8888,7 @@
         <v>40958</v>
       </c>
       <c r="E2" t="n">
-        <v>5172</v>
+        <v>5177</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -8977,7 +8914,7 @@
         <v>41306</v>
       </c>
       <c r="E3" t="n">
-        <v>4824</v>
+        <v>4829</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -9003,7 +8940,7 @@
         <v>41523</v>
       </c>
       <c r="E4" t="n">
-        <v>4607</v>
+        <v>4612</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -9029,7 +8966,7 @@
         <v>41553</v>
       </c>
       <c r="E5" t="n">
-        <v>4577</v>
+        <v>4582</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -9055,7 +8992,7 @@
         <v>41595</v>
       </c>
       <c r="E6" t="n">
-        <v>4535</v>
+        <v>4540</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -9081,7 +9018,7 @@
         <v>41722</v>
       </c>
       <c r="E7" t="n">
-        <v>4408</v>
+        <v>4413</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -9107,7 +9044,7 @@
         <v>41755</v>
       </c>
       <c r="E8" t="n">
-        <v>4375</v>
+        <v>4380</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -9133,7 +9070,7 @@
         <v>41856</v>
       </c>
       <c r="E9" t="n">
-        <v>4274</v>
+        <v>4279</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -9159,7 +9096,7 @@
         <v>41878</v>
       </c>
       <c r="E10" t="n">
-        <v>4252</v>
+        <v>4257</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -9185,7 +9122,7 @@
         <v>41927</v>
       </c>
       <c r="E11" t="n">
-        <v>4203</v>
+        <v>4208</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -9211,7 +9148,7 @@
         <v>42014</v>
       </c>
       <c r="E12" t="n">
-        <v>4116</v>
+        <v>4121</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -9237,7 +9174,7 @@
         <v>42043</v>
       </c>
       <c r="E13" t="n">
-        <v>4087</v>
+        <v>4092</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -9263,7 +9200,7 @@
         <v>42193</v>
       </c>
       <c r="E14" t="n">
-        <v>3937</v>
+        <v>3942</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -9289,7 +9226,7 @@
         <v>42201</v>
       </c>
       <c r="E15" t="n">
-        <v>3929</v>
+        <v>3934</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -9315,7 +9252,7 @@
         <v>42371</v>
       </c>
       <c r="E16" t="n">
-        <v>3759</v>
+        <v>3764</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -9341,7 +9278,7 @@
         <v>42412</v>
       </c>
       <c r="E17" t="n">
-        <v>3718</v>
+        <v>3723</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -9367,7 +9304,7 @@
         <v>42413</v>
       </c>
       <c r="E18" t="n">
-        <v>3717</v>
+        <v>3722</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -9393,7 +9330,7 @@
         <v>42418</v>
       </c>
       <c r="E19" t="n">
-        <v>3712</v>
+        <v>3717</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
@@ -9419,7 +9356,7 @@
         <v>42426</v>
       </c>
       <c r="E20" t="n">
-        <v>3704</v>
+        <v>3709</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -9445,7 +9382,7 @@
         <v>42429</v>
       </c>
       <c r="E21" t="n">
-        <v>3701</v>
+        <v>3706</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -9471,7 +9408,7 @@
         <v>42475</v>
       </c>
       <c r="E22" t="n">
-        <v>3655</v>
+        <v>3660</v>
       </c>
       <c r="F22" t="b">
         <v>1</v>
@@ -9497,7 +9434,7 @@
         <v>42483</v>
       </c>
       <c r="E23" t="n">
-        <v>3647</v>
+        <v>3652</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
@@ -9523,7 +9460,7 @@
         <v>42493</v>
       </c>
       <c r="E24" t="n">
-        <v>3637</v>
+        <v>3642</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
@@ -9549,7 +9486,7 @@
         <v>42507</v>
       </c>
       <c r="E25" t="n">
-        <v>3623</v>
+        <v>3628</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -9575,7 +9512,7 @@
         <v>42550</v>
       </c>
       <c r="E26" t="n">
-        <v>3580</v>
+        <v>3585</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -9601,7 +9538,7 @@
         <v>42675</v>
       </c>
       <c r="E27" t="n">
-        <v>3455</v>
+        <v>3460</v>
       </c>
       <c r="F27" t="b">
         <v>1</v>
@@ -9627,7 +9564,7 @@
         <v>42704</v>
       </c>
       <c r="E28" t="n">
-        <v>3426</v>
+        <v>3431</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
@@ -9653,7 +9590,7 @@
         <v>42791</v>
       </c>
       <c r="E29" t="n">
-        <v>3339</v>
+        <v>3344</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -9679,7 +9616,7 @@
         <v>42853</v>
       </c>
       <c r="E30" t="n">
-        <v>3277</v>
+        <v>3282</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -9705,7 +9642,7 @@
         <v>42874</v>
       </c>
       <c r="E31" t="n">
-        <v>3256</v>
+        <v>3261</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
@@ -9731,7 +9668,7 @@
         <v>42876</v>
       </c>
       <c r="E32" t="n">
-        <v>3254</v>
+        <v>3259</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -9757,7 +9694,7 @@
         <v>42878</v>
       </c>
       <c r="E33" t="n">
-        <v>3252</v>
+        <v>3257</v>
       </c>
       <c r="F33" t="b">
         <v>1</v>
@@ -9783,7 +9720,7 @@
         <v>42916</v>
       </c>
       <c r="E34" t="n">
-        <v>3214</v>
+        <v>3219</v>
       </c>
       <c r="F34" t="b">
         <v>1</v>
@@ -9809,7 +9746,7 @@
         <v>43008</v>
       </c>
       <c r="E35" t="n">
-        <v>3122</v>
+        <v>3127</v>
       </c>
       <c r="F35" t="b">
         <v>1</v>
@@ -9835,7 +9772,7 @@
         <v>43036</v>
       </c>
       <c r="E36" t="n">
-        <v>3094</v>
+        <v>3099</v>
       </c>
       <c r="F36" t="b">
         <v>1</v>
@@ -9861,7 +9798,7 @@
         <v>43142</v>
       </c>
       <c r="E37" t="n">
-        <v>2988</v>
+        <v>2993</v>
       </c>
       <c r="F37" t="b">
         <v>1</v>
@@ -9887,7 +9824,7 @@
         <v>43179</v>
       </c>
       <c r="E38" t="n">
-        <v>2951</v>
+        <v>2956</v>
       </c>
       <c r="F38" t="b">
         <v>1</v>
@@ -9913,7 +9850,7 @@
         <v>43229</v>
       </c>
       <c r="E39" t="n">
-        <v>2901</v>
+        <v>2906</v>
       </c>
       <c r="F39" t="b">
         <v>1</v>
@@ -9939,7 +9876,7 @@
         <v>43230</v>
       </c>
       <c r="E40" t="n">
-        <v>2900</v>
+        <v>2905</v>
       </c>
       <c r="F40" t="b">
         <v>1</v>
@@ -9965,7 +9902,7 @@
         <v>43338</v>
       </c>
       <c r="E41" t="n">
-        <v>2792</v>
+        <v>2797</v>
       </c>
       <c r="F41" t="b">
         <v>1</v>
@@ -9991,7 +9928,7 @@
         <v>43435</v>
       </c>
       <c r="E42" t="n">
-        <v>2695</v>
+        <v>2700</v>
       </c>
       <c r="F42" t="b">
         <v>1</v>
@@ -10017,7 +9954,7 @@
         <v>43463</v>
       </c>
       <c r="E43" t="n">
-        <v>2667</v>
+        <v>2672</v>
       </c>
       <c r="F43" t="b">
         <v>1</v>
@@ -10043,7 +9980,7 @@
         <v>43479</v>
       </c>
       <c r="E44" t="n">
-        <v>2651</v>
+        <v>2656</v>
       </c>
       <c r="F44" t="b">
         <v>1</v>
@@ -10069,7 +10006,7 @@
         <v>43481</v>
       </c>
       <c r="E45" t="n">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="F45" t="b">
         <v>1</v>
@@ -10095,7 +10032,7 @@
         <v>43481</v>
       </c>
       <c r="E46" t="n">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="F46" t="b">
         <v>1</v>
@@ -10121,7 +10058,7 @@
         <v>43514</v>
       </c>
       <c r="E47" t="n">
-        <v>2616</v>
+        <v>2621</v>
       </c>
       <c r="F47" t="b">
         <v>1</v>
@@ -10147,7 +10084,7 @@
         <v>43557</v>
       </c>
       <c r="E48" t="n">
-        <v>2573</v>
+        <v>2578</v>
       </c>
       <c r="F48" t="b">
         <v>1</v>
@@ -10173,7 +10110,7 @@
         <v>43567</v>
       </c>
       <c r="E49" t="n">
-        <v>2563</v>
+        <v>2568</v>
       </c>
       <c r="F49" t="b">
         <v>1</v>
@@ -10199,7 +10136,7 @@
         <v>43579</v>
       </c>
       <c r="E50" t="n">
-        <v>2551</v>
+        <v>2556</v>
       </c>
       <c r="F50" t="b">
         <v>1</v>
@@ -10225,7 +10162,7 @@
         <v>43587</v>
       </c>
       <c r="E51" t="n">
-        <v>2543</v>
+        <v>2548</v>
       </c>
       <c r="F51" t="b">
         <v>1</v>
@@ -10251,7 +10188,7 @@
         <v>43602</v>
       </c>
       <c r="E52" t="n">
-        <v>2528</v>
+        <v>2533</v>
       </c>
       <c r="F52" t="b">
         <v>1</v>
@@ -10277,7 +10214,7 @@
         <v>43627</v>
       </c>
       <c r="E53" t="n">
-        <v>2503</v>
+        <v>2508</v>
       </c>
       <c r="F53" t="b">
         <v>1</v>
@@ -10303,7 +10240,7 @@
         <v>43681</v>
       </c>
       <c r="E54" t="n">
-        <v>2449</v>
+        <v>2454</v>
       </c>
       <c r="F54" t="b">
         <v>1</v>
@@ -10329,7 +10266,7 @@
         <v>43690</v>
       </c>
       <c r="E55" t="n">
-        <v>2440</v>
+        <v>2445</v>
       </c>
       <c r="F55" t="b">
         <v>1</v>
@@ -10355,7 +10292,7 @@
         <v>43712</v>
       </c>
       <c r="E56" t="n">
-        <v>2418</v>
+        <v>2423</v>
       </c>
       <c r="F56" t="b">
         <v>1</v>
@@ -10381,7 +10318,7 @@
         <v>43718</v>
       </c>
       <c r="E57" t="n">
-        <v>2412</v>
+        <v>2417</v>
       </c>
       <c r="F57" t="b">
         <v>1</v>
@@ -10407,7 +10344,7 @@
         <v>43734</v>
       </c>
       <c r="E58" t="n">
-        <v>2396</v>
+        <v>2401</v>
       </c>
       <c r="F58" t="b">
         <v>1</v>
@@ -10433,7 +10370,7 @@
         <v>43740</v>
       </c>
       <c r="E59" t="n">
-        <v>2390</v>
+        <v>2395</v>
       </c>
       <c r="F59" t="b">
         <v>1</v>
@@ -10459,7 +10396,7 @@
         <v>43752</v>
       </c>
       <c r="E60" t="n">
-        <v>2378</v>
+        <v>2383</v>
       </c>
       <c r="F60" t="b">
         <v>1</v>
@@ -10485,7 +10422,7 @@
         <v>43763</v>
       </c>
       <c r="E61" t="n">
-        <v>2367</v>
+        <v>2372</v>
       </c>
       <c r="F61" t="b">
         <v>1</v>
@@ -10511,7 +10448,7 @@
         <v>43795</v>
       </c>
       <c r="E62" t="n">
-        <v>2335</v>
+        <v>2340</v>
       </c>
       <c r="F62" t="b">
         <v>1</v>
@@ -10537,7 +10474,7 @@
         <v>43810</v>
       </c>
       <c r="E63" t="n">
-        <v>2320</v>
+        <v>2325</v>
       </c>
       <c r="F63" t="b">
         <v>1</v>
@@ -10563,7 +10500,7 @@
         <v>43814</v>
       </c>
       <c r="E64" t="n">
-        <v>2316</v>
+        <v>2321</v>
       </c>
       <c r="F64" t="b">
         <v>1</v>
@@ -10589,7 +10526,7 @@
         <v>43852</v>
       </c>
       <c r="E65" t="n">
-        <v>2278</v>
+        <v>2283</v>
       </c>
       <c r="F65" t="b">
         <v>1</v>
@@ -10615,7 +10552,7 @@
         <v>43854</v>
       </c>
       <c r="E66" t="n">
-        <v>2276</v>
+        <v>2281</v>
       </c>
       <c r="F66" t="b">
         <v>1</v>
@@ -10641,7 +10578,7 @@
         <v>43856</v>
       </c>
       <c r="E67" t="n">
-        <v>2274</v>
+        <v>2279</v>
       </c>
       <c r="F67" t="b">
         <v>1</v>
@@ -10667,7 +10604,7 @@
         <v>43870</v>
       </c>
       <c r="E68" t="n">
-        <v>2260</v>
+        <v>2265</v>
       </c>
       <c r="F68" t="b">
         <v>1</v>
@@ -10693,7 +10630,7 @@
         <v>43899</v>
       </c>
       <c r="E69" t="n">
-        <v>2231</v>
+        <v>2236</v>
       </c>
       <c r="F69" t="b">
         <v>1</v>
@@ -10719,7 +10656,7 @@
         <v>43935</v>
       </c>
       <c r="E70" t="n">
-        <v>2195</v>
+        <v>2200</v>
       </c>
       <c r="F70" t="b">
         <v>1</v>
@@ -10745,7 +10682,7 @@
         <v>43935</v>
       </c>
       <c r="E71" t="n">
-        <v>2195</v>
+        <v>2200</v>
       </c>
       <c r="F71" t="b">
         <v>1</v>
@@ -10771,7 +10708,7 @@
         <v>43952</v>
       </c>
       <c r="E72" t="n">
-        <v>2178</v>
+        <v>2183</v>
       </c>
       <c r="F72" t="b">
         <v>1</v>
@@ -10797,7 +10734,7 @@
         <v>43957</v>
       </c>
       <c r="E73" t="n">
-        <v>2173</v>
+        <v>2178</v>
       </c>
       <c r="F73" t="b">
         <v>1</v>
@@ -10823,7 +10760,7 @@
         <v>43979</v>
       </c>
       <c r="E74" t="n">
-        <v>2151</v>
+        <v>2156</v>
       </c>
       <c r="F74" t="b">
         <v>1</v>
@@ -10849,7 +10786,7 @@
         <v>44011</v>
       </c>
       <c r="E75" t="n">
-        <v>2119</v>
+        <v>2124</v>
       </c>
       <c r="F75" t="b">
         <v>1</v>
@@ -10875,7 +10812,7 @@
         <v>44018</v>
       </c>
       <c r="E76" t="n">
-        <v>2112</v>
+        <v>2117</v>
       </c>
       <c r="F76" t="b">
         <v>1</v>
@@ -10901,7 +10838,7 @@
         <v>44075</v>
       </c>
       <c r="E77" t="n">
-        <v>2055</v>
+        <v>2060</v>
       </c>
       <c r="F77" t="b">
         <v>1</v>
@@ -10927,7 +10864,7 @@
         <v>44081</v>
       </c>
       <c r="E78" t="n">
-        <v>2049</v>
+        <v>2054</v>
       </c>
       <c r="F78" t="b">
         <v>1</v>
@@ -10953,7 +10890,7 @@
         <v>44088</v>
       </c>
       <c r="E79" t="n">
-        <v>2042</v>
+        <v>2047</v>
       </c>
       <c r="F79" t="b">
         <v>1</v>
@@ -10979,7 +10916,7 @@
         <v>44100</v>
       </c>
       <c r="E80" t="n">
-        <v>2030</v>
+        <v>2035</v>
       </c>
       <c r="F80" t="b">
         <v>1</v>
@@ -11005,7 +10942,7 @@
         <v>44100</v>
       </c>
       <c r="E81" t="n">
-        <v>2030</v>
+        <v>2035</v>
       </c>
       <c r="F81" t="b">
         <v>1</v>
@@ -11031,7 +10968,7 @@
         <v>44102</v>
       </c>
       <c r="E82" t="n">
-        <v>2028</v>
+        <v>2033</v>
       </c>
       <c r="F82" t="b">
         <v>1</v>
@@ -11057,7 +10994,7 @@
         <v>44122</v>
       </c>
       <c r="E83" t="n">
-        <v>2008</v>
+        <v>2013</v>
       </c>
       <c r="F83" t="b">
         <v>1</v>
@@ -11083,7 +11020,7 @@
         <v>44128</v>
       </c>
       <c r="E84" t="n">
-        <v>2002</v>
+        <v>2007</v>
       </c>
       <c r="F84" t="b">
         <v>1</v>
@@ -11109,7 +11046,7 @@
         <v>44131</v>
       </c>
       <c r="E85" t="n">
-        <v>1999</v>
+        <v>2004</v>
       </c>
       <c r="F85" t="b">
         <v>1</v>
@@ -11135,7 +11072,7 @@
         <v>44172</v>
       </c>
       <c r="E86" t="n">
-        <v>1958</v>
+        <v>1963</v>
       </c>
       <c r="F86" t="b">
         <v>1</v>
@@ -11161,7 +11098,7 @@
         <v>44173</v>
       </c>
       <c r="E87" t="n">
-        <v>1957</v>
+        <v>1962</v>
       </c>
       <c r="F87" t="b">
         <v>1</v>
@@ -11187,7 +11124,7 @@
         <v>44248</v>
       </c>
       <c r="E88" t="n">
-        <v>1882</v>
+        <v>1887</v>
       </c>
       <c r="F88" t="b">
         <v>1</v>
@@ -11213,7 +11150,7 @@
         <v>44267</v>
       </c>
       <c r="E89" t="n">
-        <v>1863</v>
+        <v>1868</v>
       </c>
       <c r="F89" t="b">
         <v>1</v>
@@ -11239,7 +11176,7 @@
         <v>44299</v>
       </c>
       <c r="E90" t="n">
-        <v>1831</v>
+        <v>1836</v>
       </c>
       <c r="F90" t="b">
         <v>1</v>
@@ -11265,7 +11202,7 @@
         <v>44308</v>
       </c>
       <c r="E91" t="n">
-        <v>1822</v>
+        <v>1827</v>
       </c>
       <c r="F91" t="b">
         <v>1</v>
@@ -11291,7 +11228,7 @@
         <v>44363</v>
       </c>
       <c r="E92" t="n">
-        <v>1767</v>
+        <v>1772</v>
       </c>
       <c r="F92" t="b">
         <v>1</v>
@@ -11317,7 +11254,7 @@
         <v>44368</v>
       </c>
       <c r="E93" t="n">
-        <v>1762</v>
+        <v>1767</v>
       </c>
       <c r="F93" t="b">
         <v>1</v>
@@ -11343,7 +11280,7 @@
         <v>44380</v>
       </c>
       <c r="E94" t="n">
-        <v>1750</v>
+        <v>1755</v>
       </c>
       <c r="F94" t="b">
         <v>1</v>
@@ -11369,7 +11306,7 @@
         <v>44389</v>
       </c>
       <c r="E95" t="n">
-        <v>1741</v>
+        <v>1746</v>
       </c>
       <c r="F95" t="b">
         <v>1</v>
@@ -11395,7 +11332,7 @@
         <v>44393</v>
       </c>
       <c r="E96" t="n">
-        <v>1737</v>
+        <v>1742</v>
       </c>
       <c r="F96" t="b">
         <v>1</v>
@@ -11421,7 +11358,7 @@
         <v>44401</v>
       </c>
       <c r="E97" t="n">
-        <v>1729</v>
+        <v>1734</v>
       </c>
       <c r="F97" t="b">
         <v>1</v>
@@ -11447,7 +11384,7 @@
         <v>44411</v>
       </c>
       <c r="E98" t="n">
-        <v>1719</v>
+        <v>1724</v>
       </c>
       <c r="F98" t="b">
         <v>1</v>
@@ -11473,7 +11410,7 @@
         <v>44435</v>
       </c>
       <c r="E99" t="n">
-        <v>1695</v>
+        <v>1700</v>
       </c>
       <c r="F99" t="b">
         <v>1</v>
@@ -11499,7 +11436,7 @@
         <v>44459</v>
       </c>
       <c r="E100" t="n">
-        <v>1671</v>
+        <v>1676</v>
       </c>
       <c r="F100" t="b">
         <v>1</v>
@@ -11525,7 +11462,7 @@
         <v>44468</v>
       </c>
       <c r="E101" t="n">
-        <v>1662</v>
+        <v>1667</v>
       </c>
       <c r="F101" t="b">
         <v>1</v>
@@ -11551,7 +11488,7 @@
         <v>44479</v>
       </c>
       <c r="E102" t="n">
-        <v>1651</v>
+        <v>1656</v>
       </c>
       <c r="F102" t="b">
         <v>1</v>
@@ -11577,7 +11514,7 @@
         <v>44483</v>
       </c>
       <c r="E103" t="n">
-        <v>1647</v>
+        <v>1652</v>
       </c>
       <c r="F103" t="b">
         <v>1</v>
@@ -11603,7 +11540,7 @@
         <v>44486</v>
       </c>
       <c r="E104" t="n">
-        <v>1644</v>
+        <v>1649</v>
       </c>
       <c r="F104" t="b">
         <v>1</v>
@@ -11629,7 +11566,7 @@
         <v>44497</v>
       </c>
       <c r="E105" t="n">
-        <v>1633</v>
+        <v>1638</v>
       </c>
       <c r="F105" t="b">
         <v>1</v>
@@ -11655,7 +11592,7 @@
         <v>44508</v>
       </c>
       <c r="E106" t="n">
-        <v>1622</v>
+        <v>1627</v>
       </c>
       <c r="F106" t="b">
         <v>1</v>
@@ -11681,7 +11618,7 @@
         <v>44509</v>
       </c>
       <c r="E107" t="n">
-        <v>1621</v>
+        <v>1626</v>
       </c>
       <c r="F107" t="b">
         <v>1</v>
@@ -11707,7 +11644,7 @@
         <v>44511</v>
       </c>
       <c r="E108" t="n">
-        <v>1619</v>
+        <v>1624</v>
       </c>
       <c r="F108" t="b">
         <v>1</v>
@@ -11733,7 +11670,7 @@
         <v>44522</v>
       </c>
       <c r="E109" t="n">
-        <v>1608</v>
+        <v>1613</v>
       </c>
       <c r="F109" t="b">
         <v>1</v>
@@ -11759,7 +11696,7 @@
         <v>44528</v>
       </c>
       <c r="E110" t="n">
-        <v>1602</v>
+        <v>1607</v>
       </c>
       <c r="F110" t="b">
         <v>1</v>
@@ -11785,7 +11722,7 @@
         <v>44528</v>
       </c>
       <c r="E111" t="n">
-        <v>1602</v>
+        <v>1607</v>
       </c>
       <c r="F111" t="b">
         <v>1</v>
@@ -11811,7 +11748,7 @@
         <v>44536</v>
       </c>
       <c r="E112" t="n">
-        <v>1594</v>
+        <v>1599</v>
       </c>
       <c r="F112" t="b">
         <v>1</v>
@@ -11837,7 +11774,7 @@
         <v>44537</v>
       </c>
       <c r="E113" t="n">
-        <v>1593</v>
+        <v>1598</v>
       </c>
       <c r="F113" t="b">
         <v>1</v>
@@ -11863,7 +11800,7 @@
         <v>44540</v>
       </c>
       <c r="E114" t="n">
-        <v>1590</v>
+        <v>1595</v>
       </c>
       <c r="F114" t="b">
         <v>1</v>
@@ -11889,7 +11826,7 @@
         <v>44549</v>
       </c>
       <c r="E115" t="n">
-        <v>1581</v>
+        <v>1586</v>
       </c>
       <c r="F115" t="b">
         <v>1</v>
@@ -11915,7 +11852,7 @@
         <v>44551</v>
       </c>
       <c r="E116" t="n">
-        <v>1579</v>
+        <v>1584</v>
       </c>
       <c r="F116" t="b">
         <v>1</v>
@@ -11941,7 +11878,7 @@
         <v>44555</v>
       </c>
       <c r="E117" t="n">
-        <v>1575</v>
+        <v>1580</v>
       </c>
       <c r="F117" t="b">
         <v>1</v>
@@ -11967,7 +11904,7 @@
         <v>44557</v>
       </c>
       <c r="E118" t="n">
-        <v>1573</v>
+        <v>1578</v>
       </c>
       <c r="F118" t="b">
         <v>1</v>
@@ -11993,7 +11930,7 @@
         <v>44574</v>
       </c>
       <c r="E119" t="n">
-        <v>1556</v>
+        <v>1561</v>
       </c>
       <c r="F119" t="b">
         <v>1</v>
@@ -12019,7 +11956,7 @@
         <v>44576</v>
       </c>
       <c r="E120" t="n">
-        <v>1554</v>
+        <v>1559</v>
       </c>
       <c r="F120" t="b">
         <v>1</v>
@@ -12045,7 +11982,7 @@
         <v>44596</v>
       </c>
       <c r="E121" t="n">
-        <v>1534</v>
+        <v>1539</v>
       </c>
       <c r="F121" t="b">
         <v>1</v>
@@ -12071,7 +12008,7 @@
         <v>44651</v>
       </c>
       <c r="E122" t="n">
-        <v>1479</v>
+        <v>1484</v>
       </c>
       <c r="F122" t="b">
         <v>1</v>
@@ -12097,7 +12034,7 @@
         <v>44657</v>
       </c>
       <c r="E123" t="n">
-        <v>1473</v>
+        <v>1478</v>
       </c>
       <c r="F123" t="b">
         <v>1</v>
@@ -12123,7 +12060,7 @@
         <v>44672</v>
       </c>
       <c r="E124" t="n">
-        <v>1458</v>
+        <v>1463</v>
       </c>
       <c r="F124" t="b">
         <v>1</v>
@@ -12149,7 +12086,7 @@
         <v>44686</v>
       </c>
       <c r="E125" t="n">
-        <v>1444</v>
+        <v>1449</v>
       </c>
       <c r="F125" t="b">
         <v>1</v>
@@ -12175,7 +12112,7 @@
         <v>44691</v>
       </c>
       <c r="E126" t="n">
-        <v>1439</v>
+        <v>1444</v>
       </c>
       <c r="F126" t="b">
         <v>1</v>
@@ -12201,7 +12138,7 @@
         <v>44694</v>
       </c>
       <c r="E127" t="n">
-        <v>1436</v>
+        <v>1441</v>
       </c>
       <c r="F127" t="b">
         <v>1</v>
@@ -12227,7 +12164,7 @@
         <v>44696</v>
       </c>
       <c r="E128" t="n">
-        <v>1434</v>
+        <v>1439</v>
       </c>
       <c r="F128" t="b">
         <v>1</v>
@@ -12253,7 +12190,7 @@
         <v>44719</v>
       </c>
       <c r="E129" t="n">
-        <v>1411</v>
+        <v>1416</v>
       </c>
       <c r="F129" t="b">
         <v>1</v>
@@ -12279,7 +12216,7 @@
         <v>44724</v>
       </c>
       <c r="E130" t="n">
-        <v>1406</v>
+        <v>1411</v>
       </c>
       <c r="F130" t="b">
         <v>1</v>
@@ -12305,7 +12242,7 @@
         <v>44728</v>
       </c>
       <c r="E131" t="n">
-        <v>1402</v>
+        <v>1407</v>
       </c>
       <c r="F131" t="b">
         <v>1</v>
@@ -12331,7 +12268,7 @@
         <v>44742</v>
       </c>
       <c r="E132" t="n">
-        <v>1388</v>
+        <v>1393</v>
       </c>
       <c r="F132" t="b">
         <v>1</v>
@@ -12357,7 +12294,7 @@
         <v>44747</v>
       </c>
       <c r="E133" t="n">
-        <v>1383</v>
+        <v>1388</v>
       </c>
       <c r="F133" t="b">
         <v>1</v>
@@ -12383,7 +12320,7 @@
         <v>44747</v>
       </c>
       <c r="E134" t="n">
-        <v>1383</v>
+        <v>1388</v>
       </c>
       <c r="F134" t="b">
         <v>1</v>
@@ -12409,7 +12346,7 @@
         <v>44759</v>
       </c>
       <c r="E135" t="n">
-        <v>1371</v>
+        <v>1376</v>
       </c>
       <c r="F135" t="b">
         <v>1</v>
@@ -12435,7 +12372,7 @@
         <v>44762</v>
       </c>
       <c r="E136" t="n">
-        <v>1368</v>
+        <v>1373</v>
       </c>
       <c r="F136" t="b">
         <v>1</v>
@@ -12461,7 +12398,7 @@
         <v>44794</v>
       </c>
       <c r="E137" t="n">
-        <v>1336</v>
+        <v>1341</v>
       </c>
       <c r="F137" t="b">
         <v>1</v>
@@ -12487,7 +12424,7 @@
         <v>44810</v>
       </c>
       <c r="E138" t="n">
-        <v>1320</v>
+        <v>1325</v>
       </c>
       <c r="F138" t="b">
         <v>1</v>
@@ -12513,7 +12450,7 @@
         <v>44810</v>
       </c>
       <c r="E139" t="n">
-        <v>1320</v>
+        <v>1325</v>
       </c>
       <c r="F139" t="b">
         <v>1</v>
@@ -12539,7 +12476,7 @@
         <v>44817</v>
       </c>
       <c r="E140" t="n">
-        <v>1313</v>
+        <v>1318</v>
       </c>
       <c r="F140" t="b">
         <v>1</v>
@@ -12565,7 +12502,7 @@
         <v>44819</v>
       </c>
       <c r="E141" t="n">
-        <v>1311</v>
+        <v>1316</v>
       </c>
       <c r="F141" t="b">
         <v>1</v>
@@ -12591,7 +12528,7 @@
         <v>44821</v>
       </c>
       <c r="E142" t="n">
-        <v>1309</v>
+        <v>1314</v>
       </c>
       <c r="F142" t="b">
         <v>1</v>
@@ -12617,7 +12554,7 @@
         <v>44863</v>
       </c>
       <c r="E143" t="n">
-        <v>1267</v>
+        <v>1272</v>
       </c>
       <c r="F143" t="b">
         <v>1</v>
@@ -12643,7 +12580,7 @@
         <v>44880</v>
       </c>
       <c r="E144" t="n">
-        <v>1250</v>
+        <v>1255</v>
       </c>
       <c r="F144" t="b">
         <v>1</v>
@@ -12669,7 +12606,7 @@
         <v>44897</v>
       </c>
       <c r="E145" t="n">
-        <v>1233</v>
+        <v>1238</v>
       </c>
       <c r="F145" t="b">
         <v>1</v>
@@ -12695,7 +12632,7 @@
         <v>44897</v>
       </c>
       <c r="E146" t="n">
-        <v>1233</v>
+        <v>1238</v>
       </c>
       <c r="F146" t="b">
         <v>1</v>
@@ -12721,7 +12658,7 @@
         <v>44897</v>
       </c>
       <c r="E147" t="n">
-        <v>1233</v>
+        <v>1238</v>
       </c>
       <c r="F147" t="b">
         <v>1</v>
@@ -12747,7 +12684,7 @@
         <v>44917</v>
       </c>
       <c r="E148" t="n">
-        <v>1213</v>
+        <v>1218</v>
       </c>
       <c r="F148" t="b">
         <v>1</v>
@@ -12773,7 +12710,7 @@
         <v>44922</v>
       </c>
       <c r="E149" t="n">
-        <v>1208</v>
+        <v>1213</v>
       </c>
       <c r="F149" t="b">
         <v>1</v>
@@ -12799,7 +12736,7 @@
         <v>44928</v>
       </c>
       <c r="E150" t="n">
-        <v>1202</v>
+        <v>1207</v>
       </c>
       <c r="F150" t="b">
         <v>1</v>
@@ -12825,7 +12762,7 @@
         <v>44928</v>
       </c>
       <c r="E151" t="n">
-        <v>1202</v>
+        <v>1207</v>
       </c>
       <c r="F151" t="b">
         <v>1</v>
@@ -12851,7 +12788,7 @@
         <v>44970</v>
       </c>
       <c r="E152" t="n">
-        <v>1160</v>
+        <v>1165</v>
       </c>
       <c r="F152" t="b">
         <v>1</v>
@@ -12877,7 +12814,7 @@
         <v>44975</v>
       </c>
       <c r="E153" t="n">
-        <v>1155</v>
+        <v>1160</v>
       </c>
       <c r="F153" t="b">
         <v>1</v>
@@ -12903,7 +12840,7 @@
         <v>44983</v>
       </c>
       <c r="E154" t="n">
-        <v>1147</v>
+        <v>1152</v>
       </c>
       <c r="F154" t="b">
         <v>1</v>
@@ -12929,7 +12866,7 @@
         <v>44984</v>
       </c>
       <c r="E155" t="n">
-        <v>1146</v>
+        <v>1151</v>
       </c>
       <c r="F155" t="b">
         <v>1</v>
@@ -12955,7 +12892,7 @@
         <v>45008</v>
       </c>
       <c r="E156" t="n">
-        <v>1122</v>
+        <v>1127</v>
       </c>
       <c r="F156" t="b">
         <v>1</v>
@@ -12981,7 +12918,7 @@
         <v>45011</v>
       </c>
       <c r="E157" t="n">
-        <v>1119</v>
+        <v>1124</v>
       </c>
       <c r="F157" t="b">
         <v>1</v>
@@ -13007,7 +12944,7 @@
         <v>45019</v>
       </c>
       <c r="E158" t="n">
-        <v>1111</v>
+        <v>1116</v>
       </c>
       <c r="F158" t="b">
         <v>1</v>
@@ -13033,7 +12970,7 @@
         <v>45025</v>
       </c>
       <c r="E159" t="n">
-        <v>1105</v>
+        <v>1110</v>
       </c>
       <c r="F159" t="b">
         <v>1</v>
@@ -13059,7 +12996,7 @@
         <v>45027</v>
       </c>
       <c r="E160" t="n">
-        <v>1103</v>
+        <v>1108</v>
       </c>
       <c r="F160" t="b">
         <v>1</v>
@@ -13085,7 +13022,7 @@
         <v>45051</v>
       </c>
       <c r="E161" t="n">
-        <v>1079</v>
+        <v>1084</v>
       </c>
       <c r="F161" t="b">
         <v>1</v>
@@ -13111,7 +13048,7 @@
         <v>45056</v>
       </c>
       <c r="E162" t="n">
-        <v>1074</v>
+        <v>1079</v>
       </c>
       <c r="F162" t="b">
         <v>1</v>
@@ -13137,7 +13074,7 @@
         <v>45060</v>
       </c>
       <c r="E163" t="n">
-        <v>1070</v>
+        <v>1075</v>
       </c>
       <c r="F163" t="b">
         <v>1</v>
@@ -13163,7 +13100,7 @@
         <v>45070</v>
       </c>
       <c r="E164" t="n">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="F164" t="b">
         <v>1</v>
@@ -13189,7 +13126,7 @@
         <v>45076</v>
       </c>
       <c r="E165" t="n">
-        <v>1054</v>
+        <v>1059</v>
       </c>
       <c r="F165" t="b">
         <v>1</v>
@@ -13215,7 +13152,7 @@
         <v>45104</v>
       </c>
       <c r="E166" t="n">
-        <v>1026</v>
+        <v>1031</v>
       </c>
       <c r="F166" t="b">
         <v>1</v>
@@ -13241,7 +13178,7 @@
         <v>45110</v>
       </c>
       <c r="E167" t="n">
-        <v>1020</v>
+        <v>1025</v>
       </c>
       <c r="F167" t="b">
         <v>1</v>
@@ -13267,7 +13204,7 @@
         <v>45124</v>
       </c>
       <c r="E168" t="n">
-        <v>1006</v>
+        <v>1011</v>
       </c>
       <c r="F168" t="b">
         <v>1</v>
@@ -13293,7 +13230,7 @@
         <v>45151</v>
       </c>
       <c r="E169" t="n">
-        <v>979</v>
+        <v>984</v>
       </c>
       <c r="F169" t="b">
         <v>1</v>
@@ -13319,7 +13256,7 @@
         <v>45165</v>
       </c>
       <c r="E170" t="n">
-        <v>965</v>
+        <v>970</v>
       </c>
       <c r="F170" t="b">
         <v>1</v>
@@ -13345,7 +13282,7 @@
         <v>45165</v>
       </c>
       <c r="E171" t="n">
-        <v>965</v>
+        <v>970</v>
       </c>
       <c r="F171" t="b">
         <v>1</v>
@@ -13371,7 +13308,7 @@
         <v>45167</v>
       </c>
       <c r="E172" t="n">
-        <v>963</v>
+        <v>968</v>
       </c>
       <c r="F172" t="b">
         <v>1</v>
@@ -13397,7 +13334,7 @@
         <v>45170</v>
       </c>
       <c r="E173" t="n">
-        <v>960</v>
+        <v>965</v>
       </c>
       <c r="F173" t="b">
         <v>1</v>
@@ -13423,7 +13360,7 @@
         <v>45181</v>
       </c>
       <c r="E174" t="n">
-        <v>949</v>
+        <v>954</v>
       </c>
       <c r="F174" t="b">
         <v>1</v>
@@ -13449,7 +13386,7 @@
         <v>45183</v>
       </c>
       <c r="E175" t="n">
-        <v>947</v>
+        <v>952</v>
       </c>
       <c r="F175" t="b">
         <v>1</v>
@@ -13475,7 +13412,7 @@
         <v>45186</v>
       </c>
       <c r="E176" t="n">
-        <v>944</v>
+        <v>949</v>
       </c>
       <c r="F176" t="b">
         <v>1</v>
@@ -13501,7 +13438,7 @@
         <v>45187</v>
       </c>
       <c r="E177" t="n">
-        <v>943</v>
+        <v>948</v>
       </c>
       <c r="F177" t="b">
         <v>1</v>
@@ -13527,7 +13464,7 @@
         <v>45197</v>
       </c>
       <c r="E178" t="n">
-        <v>933</v>
+        <v>938</v>
       </c>
       <c r="F178" t="b">
         <v>1</v>
@@ -13553,7 +13490,7 @@
         <v>45201</v>
       </c>
       <c r="E179" t="n">
-        <v>929</v>
+        <v>934</v>
       </c>
       <c r="F179" t="b">
         <v>1</v>
@@ -13579,7 +13516,7 @@
         <v>45204</v>
       </c>
       <c r="E180" t="n">
-        <v>926</v>
+        <v>931</v>
       </c>
       <c r="F180" t="b">
         <v>1</v>
@@ -13605,7 +13542,7 @@
         <v>45206</v>
       </c>
       <c r="E181" t="n">
-        <v>924</v>
+        <v>929</v>
       </c>
       <c r="F181" t="b">
         <v>1</v>
@@ -13631,7 +13568,7 @@
         <v>45218</v>
       </c>
       <c r="E182" t="n">
-        <v>912</v>
+        <v>917</v>
       </c>
       <c r="F182" t="b">
         <v>1</v>
@@ -13657,7 +13594,7 @@
         <v>45225</v>
       </c>
       <c r="E183" t="n">
-        <v>905</v>
+        <v>910</v>
       </c>
       <c r="F183" t="b">
         <v>1</v>
@@ -13683,7 +13620,7 @@
         <v>45233</v>
       </c>
       <c r="E184" t="n">
-        <v>897</v>
+        <v>902</v>
       </c>
       <c r="F184" t="b">
         <v>1</v>
@@ -13709,7 +13646,7 @@
         <v>45235</v>
       </c>
       <c r="E185" t="n">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="F185" t="b">
         <v>1</v>
@@ -13735,7 +13672,7 @@
         <v>45237</v>
       </c>
       <c r="E186" t="n">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="F186" t="b">
         <v>1</v>
@@ -13761,7 +13698,7 @@
         <v>45244</v>
       </c>
       <c r="E187" t="n">
-        <v>886</v>
+        <v>891</v>
       </c>
       <c r="F187" t="b">
         <v>1</v>
@@ -13787,7 +13724,7 @@
         <v>45248</v>
       </c>
       <c r="E188" t="n">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F188" t="b">
         <v>1</v>
@@ -13813,7 +13750,7 @@
         <v>45263</v>
       </c>
       <c r="E189" t="n">
-        <v>867</v>
+        <v>872</v>
       </c>
       <c r="F189" t="b">
         <v>1</v>
@@ -13839,7 +13776,7 @@
         <v>45263</v>
       </c>
       <c r="E190" t="n">
-        <v>867</v>
+        <v>872</v>
       </c>
       <c r="F190" t="b">
         <v>1</v>
@@ -13865,7 +13802,7 @@
         <v>45274</v>
       </c>
       <c r="E191" t="n">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="F191" t="b">
         <v>1</v>
@@ -13891,7 +13828,7 @@
         <v>45275</v>
       </c>
       <c r="E192" t="n">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="F192" t="b">
         <v>1</v>
@@ -13917,7 +13854,7 @@
         <v>45278</v>
       </c>
       <c r="E193" t="n">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="F193" t="b">
         <v>1</v>
@@ -13943,7 +13880,7 @@
         <v>45305</v>
       </c>
       <c r="E194" t="n">
-        <v>825</v>
+        <v>830</v>
       </c>
       <c r="F194" t="b">
         <v>1</v>
@@ -13969,7 +13906,7 @@
         <v>45325</v>
       </c>
       <c r="E195" t="n">
-        <v>805</v>
+        <v>810</v>
       </c>
       <c r="F195" t="b">
         <v>1</v>
@@ -13995,7 +13932,7 @@
         <v>45328</v>
       </c>
       <c r="E196" t="n">
-        <v>802</v>
+        <v>807</v>
       </c>
       <c r="F196" t="b">
         <v>1</v>
@@ -14021,7 +13958,7 @@
         <v>45346</v>
       </c>
       <c r="E197" t="n">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="F197" t="b">
         <v>1</v>
@@ -14047,7 +13984,7 @@
         <v>45358</v>
       </c>
       <c r="E198" t="n">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="F198" t="b">
         <v>1</v>
@@ -14073,7 +14010,7 @@
         <v>45363</v>
       </c>
       <c r="E199" t="n">
-        <v>767</v>
+        <v>772</v>
       </c>
       <c r="F199" t="b">
         <v>1</v>
@@ -14099,7 +14036,7 @@
         <v>45364</v>
       </c>
       <c r="E200" t="n">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="F200" t="b">
         <v>1</v>
@@ -14125,7 +14062,7 @@
         <v>45370</v>
       </c>
       <c r="E201" t="n">
-        <v>760</v>
+        <v>765</v>
       </c>
       <c r="F201" t="b">
         <v>1</v>
@@ -14151,7 +14088,7 @@
         <v>45373</v>
       </c>
       <c r="E202" t="n">
-        <v>757</v>
+        <v>762</v>
       </c>
       <c r="F202" t="b">
         <v>1</v>
@@ -14177,7 +14114,7 @@
         <v>45385</v>
       </c>
       <c r="E203" t="n">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="F203" t="b">
         <v>1</v>
@@ -14203,7 +14140,7 @@
         <v>45388</v>
       </c>
       <c r="E204" t="n">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="F204" t="b">
         <v>1</v>
@@ -14229,7 +14166,7 @@
         <v>45391</v>
       </c>
       <c r="E205" t="n">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="F205" t="b">
         <v>1</v>
@@ -14255,7 +14192,7 @@
         <v>45401</v>
       </c>
       <c r="E206" t="n">
-        <v>729</v>
+        <v>734</v>
       </c>
       <c r="F206" t="b">
         <v>1</v>
@@ -14281,7 +14218,7 @@
         <v>45415</v>
       </c>
       <c r="E207" t="n">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="F207" t="b">
         <v>1</v>
@@ -14307,7 +14244,7 @@
         <v>45427</v>
       </c>
       <c r="E208" t="n">
-        <v>703</v>
+        <v>708</v>
       </c>
       <c r="F208" t="b">
         <v>1</v>
@@ -14333,7 +14270,7 @@
         <v>45429</v>
       </c>
       <c r="E209" t="n">
-        <v>701</v>
+        <v>706</v>
       </c>
       <c r="F209" t="b">
         <v>1</v>
@@ -14359,7 +14296,7 @@
         <v>45431</v>
       </c>
       <c r="E210" t="n">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="F210" t="b">
         <v>1</v>
@@ -14385,7 +14322,7 @@
         <v>45433</v>
       </c>
       <c r="E211" t="n">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="F211" t="b">
         <v>1</v>
@@ -14411,7 +14348,7 @@
         <v>45448</v>
       </c>
       <c r="E212" t="n">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="F212" t="b">
         <v>1</v>
@@ -14437,7 +14374,7 @@
         <v>45451</v>
       </c>
       <c r="E213" t="n">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="F213" t="b">
         <v>1</v>
@@ -14463,7 +14400,7 @@
         <v>45464</v>
       </c>
       <c r="E214" t="n">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="F214" t="b">
         <v>1</v>
@@ -14489,7 +14426,7 @@
         <v>45470</v>
       </c>
       <c r="E215" t="n">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="F215" t="b">
         <v>1</v>
@@ -14515,7 +14452,7 @@
         <v>45478</v>
       </c>
       <c r="E216" t="n">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="F216" t="b">
         <v>1</v>
@@ -14541,7 +14478,7 @@
         <v>45502</v>
       </c>
       <c r="E217" t="n">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="F217" t="b">
         <v>1</v>
@@ -14567,7 +14504,7 @@
         <v>45503</v>
       </c>
       <c r="E218" t="n">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="F218" t="b">
         <v>1</v>
@@ -14593,7 +14530,7 @@
         <v>45504</v>
       </c>
       <c r="E219" t="n">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="F219" t="b">
         <v>1</v>
@@ -14619,7 +14556,7 @@
         <v>45511</v>
       </c>
       <c r="E220" t="n">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="F220" t="b">
         <v>1</v>
@@ -14645,7 +14582,7 @@
         <v>45513</v>
       </c>
       <c r="E221" t="n">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="F221" t="b">
         <v>1</v>
@@ -14671,7 +14608,7 @@
         <v>45531</v>
       </c>
       <c r="E222" t="n">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="F222" t="b">
         <v>1</v>
@@ -14697,7 +14634,7 @@
         <v>45535</v>
       </c>
       <c r="E223" t="n">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="F223" t="b">
         <v>1</v>
@@ -14723,7 +14660,7 @@
         <v>45538</v>
       </c>
       <c r="E224" t="n">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="F224" t="b">
         <v>1</v>
@@ -14749,7 +14686,7 @@
         <v>45541</v>
       </c>
       <c r="E225" t="n">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="F225" t="b">
         <v>1</v>
@@ -14775,7 +14712,7 @@
         <v>45542</v>
       </c>
       <c r="E226" t="n">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="F226" t="b">
         <v>1</v>
@@ -14801,7 +14738,7 @@
         <v>45545</v>
       </c>
       <c r="E227" t="n">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="F227" t="b">
         <v>1</v>
@@ -14827,7 +14764,7 @@
         <v>45554</v>
       </c>
       <c r="E228" t="n">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="F228" t="b">
         <v>1</v>
@@ -14853,7 +14790,7 @@
         <v>45556</v>
       </c>
       <c r="E229" t="n">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="F229" t="b">
         <v>1</v>
@@ -14879,7 +14816,7 @@
         <v>45558</v>
       </c>
       <c r="E230" t="n">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="F230" t="b">
         <v>1</v>
@@ -14905,7 +14842,7 @@
         <v>45558</v>
       </c>
       <c r="E231" t="n">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="F231" t="b">
         <v>1</v>
@@ -14931,7 +14868,7 @@
         <v>45558</v>
       </c>
       <c r="E232" t="n">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="F232" t="b">
         <v>1</v>
@@ -14957,7 +14894,7 @@
         <v>45566</v>
       </c>
       <c r="E233" t="n">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="F233" t="b">
         <v>1</v>
@@ -14983,7 +14920,7 @@
         <v>45583</v>
       </c>
       <c r="E234" t="n">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="F234" t="b">
         <v>1</v>
@@ -15009,7 +14946,7 @@
         <v>45583</v>
       </c>
       <c r="E235" t="n">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="F235" t="b">
         <v>1</v>
@@ -15035,7 +14972,7 @@
         <v>45587</v>
       </c>
       <c r="E236" t="n">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="F236" t="b">
         <v>1</v>
@@ -15061,7 +14998,7 @@
         <v>45591</v>
       </c>
       <c r="E237" t="n">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="F237" t="b">
         <v>1</v>
@@ -15087,7 +15024,7 @@
         <v>45594</v>
       </c>
       <c r="E238" t="n">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="F238" t="b">
         <v>1</v>
@@ -15113,7 +15050,7 @@
         <v>45594</v>
       </c>
       <c r="E239" t="n">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="F239" t="b">
         <v>1</v>
@@ -15139,7 +15076,7 @@
         <v>45601</v>
       </c>
       <c r="E240" t="n">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="F240" t="b">
         <v>1</v>
@@ -15165,7 +15102,7 @@
         <v>45607</v>
       </c>
       <c r="E241" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="F241" t="b">
         <v>1</v>
@@ -15191,7 +15128,7 @@
         <v>45609</v>
       </c>
       <c r="E242" t="n">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="F242" t="b">
         <v>1</v>
@@ -15217,7 +15154,7 @@
         <v>45612</v>
       </c>
       <c r="E243" t="n">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="F243" t="b">
         <v>1</v>
@@ -15243,7 +15180,7 @@
         <v>45616</v>
       </c>
       <c r="E244" t="n">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="F244" t="b">
         <v>1</v>
@@ -15269,7 +15206,7 @@
         <v>45619</v>
       </c>
       <c r="E245" t="n">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="F245" t="b">
         <v>1</v>
@@ -15295,7 +15232,7 @@
         <v>45627</v>
       </c>
       <c r="E246" t="n">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="F246" t="b">
         <v>1</v>
@@ -15321,7 +15258,7 @@
         <v>45629</v>
       </c>
       <c r="E247" t="n">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="F247" t="b">
         <v>1</v>
@@ -15347,7 +15284,7 @@
         <v>45634</v>
       </c>
       <c r="E248" t="n">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="F248" t="b">
         <v>1</v>
@@ -15373,7 +15310,7 @@
         <v>45634</v>
       </c>
       <c r="E249" t="n">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="F249" t="b">
         <v>1</v>
@@ -15399,7 +15336,7 @@
         <v>45639</v>
       </c>
       <c r="E250" t="n">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="F250" t="b">
         <v>1</v>
@@ -15425,7 +15362,7 @@
         <v>45642</v>
       </c>
       <c r="E251" t="n">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="F251" t="b">
         <v>1</v>
@@ -15451,7 +15388,7 @@
         <v>45648</v>
       </c>
       <c r="E252" t="n">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="F252" t="b">
         <v>1</v>
@@ -15477,7 +15414,7 @@
         <v>45649</v>
       </c>
       <c r="E253" t="n">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="F253" t="b">
         <v>1</v>
@@ -15503,7 +15440,7 @@
         <v>45649</v>
       </c>
       <c r="E254" t="n">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="F254" t="b">
         <v>1</v>
@@ -15529,7 +15466,7 @@
         <v>45682</v>
       </c>
       <c r="E255" t="n">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="F255" t="b">
         <v>1</v>
@@ -15555,7 +15492,7 @@
         <v>45696</v>
       </c>
       <c r="E256" t="n">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="F256" t="b">
         <v>1</v>
@@ -15581,7 +15518,7 @@
         <v>45698</v>
       </c>
       <c r="E257" t="n">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="F257" t="b">
         <v>1</v>
@@ -15607,7 +15544,7 @@
         <v>45699</v>
       </c>
       <c r="E258" t="n">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="F258" t="b">
         <v>1</v>
@@ -15633,7 +15570,7 @@
         <v>45703</v>
       </c>
       <c r="E259" t="n">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="F259" t="b">
         <v>1</v>
@@ -15659,7 +15596,7 @@
         <v>45704</v>
       </c>
       <c r="E260" t="n">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="F260" t="b">
         <v>1</v>
@@ -15685,7 +15622,7 @@
         <v>45711</v>
       </c>
       <c r="E261" t="n">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="F261" t="b">
         <v>1</v>
@@ -15711,7 +15648,7 @@
         <v>45712</v>
       </c>
       <c r="E262" t="n">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="F262" t="b">
         <v>1</v>
@@ -15737,7 +15674,7 @@
         <v>45712</v>
       </c>
       <c r="E263" t="n">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="F263" t="b">
         <v>1</v>
@@ -15763,7 +15700,7 @@
         <v>45712</v>
       </c>
       <c r="E264" t="n">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="F264" t="b">
         <v>1</v>
@@ -15789,7 +15726,7 @@
         <v>45715</v>
       </c>
       <c r="E265" t="n">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="F265" t="b">
         <v>1</v>
@@ -15815,7 +15752,7 @@
         <v>45717</v>
       </c>
       <c r="E266" t="n">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="F266" t="b">
         <v>1</v>
@@ -15841,7 +15778,7 @@
         <v>45720</v>
       </c>
       <c r="E267" t="n">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="F267" t="b">
         <v>1</v>
@@ -15867,7 +15804,7 @@
         <v>45730</v>
       </c>
       <c r="E268" t="n">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="F268" t="b">
         <v>1</v>
@@ -15893,7 +15830,7 @@
         <v>45730</v>
       </c>
       <c r="E269" t="n">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="F269" t="b">
         <v>1</v>
@@ -15919,7 +15856,7 @@
         <v>45736</v>
       </c>
       <c r="E270" t="n">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="F270" t="b">
         <v>1</v>
@@ -15945,7 +15882,7 @@
         <v>45742</v>
       </c>
       <c r="E271" t="n">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="F271" t="b">
         <v>1</v>
@@ -15971,7 +15908,7 @@
         <v>45747</v>
       </c>
       <c r="E272" t="n">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="F272" t="b">
         <v>1</v>
@@ -15997,7 +15934,7 @@
         <v>45748</v>
       </c>
       <c r="E273" t="n">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="F273" t="b">
         <v>1</v>
@@ -16023,10 +15960,10 @@
         <v>45765</v>
       </c>
       <c r="E274" t="n">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="F274" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="275">
@@ -16049,10 +15986,10 @@
         <v>45767</v>
       </c>
       <c r="E275" t="n">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="F275" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="276">
@@ -16075,7 +16012,7 @@
         <v>45774</v>
       </c>
       <c r="E276" t="n">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="F276" t="b">
         <v>0</v>
@@ -16101,7 +16038,7 @@
         <v>45780</v>
       </c>
       <c r="E277" t="n">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="F277" t="b">
         <v>0</v>
@@ -16127,7 +16064,7 @@
         <v>45783</v>
       </c>
       <c r="E278" t="n">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="F278" t="b">
         <v>0</v>
@@ -16153,7 +16090,7 @@
         <v>45789</v>
       </c>
       <c r="E279" t="n">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="F279" t="b">
         <v>0</v>
@@ -16179,7 +16116,7 @@
         <v>45801</v>
       </c>
       <c r="E280" t="n">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="F280" t="b">
         <v>0</v>
@@ -16205,7 +16142,7 @@
         <v>45805</v>
       </c>
       <c r="E281" t="n">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="F281" t="b">
         <v>0</v>
@@ -16231,7 +16168,7 @@
         <v>45814</v>
       </c>
       <c r="E282" t="n">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="F282" t="b">
         <v>0</v>
@@ -16257,7 +16194,7 @@
         <v>45819</v>
       </c>
       <c r="E283" t="n">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="F283" t="b">
         <v>0</v>
@@ -16283,7 +16220,7 @@
         <v>45821</v>
       </c>
       <c r="E284" t="n">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="F284" t="b">
         <v>0</v>
@@ -16309,7 +16246,7 @@
         <v>45833</v>
       </c>
       <c r="E285" t="n">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="F285" t="b">
         <v>0</v>
@@ -16335,7 +16272,7 @@
         <v>45834</v>
       </c>
       <c r="E286" t="n">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="F286" t="b">
         <v>0</v>
@@ -16361,7 +16298,7 @@
         <v>45834</v>
       </c>
       <c r="E287" t="n">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="F287" t="b">
         <v>0</v>
@@ -16387,7 +16324,7 @@
         <v>45848</v>
       </c>
       <c r="E288" t="n">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="F288" t="b">
         <v>0</v>
@@ -16413,7 +16350,7 @@
         <v>45856</v>
       </c>
       <c r="E289" t="n">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="F289" t="b">
         <v>0</v>
@@ -16439,7 +16376,7 @@
         <v>45857</v>
       </c>
       <c r="E290" t="n">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="F290" t="b">
         <v>0</v>
@@ -16465,7 +16402,7 @@
         <v>45858</v>
       </c>
       <c r="E291" t="n">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="F291" t="b">
         <v>0</v>
@@ -16491,7 +16428,7 @@
         <v>45860</v>
       </c>
       <c r="E292" t="n">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="F292" t="b">
         <v>0</v>
@@ -16517,7 +16454,7 @@
         <v>45864</v>
       </c>
       <c r="E293" t="n">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="F293" t="b">
         <v>0</v>
@@ -16543,7 +16480,7 @@
         <v>45873</v>
       </c>
       <c r="E294" t="n">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F294" t="b">
         <v>0</v>
@@ -16569,7 +16506,7 @@
         <v>45888</v>
       </c>
       <c r="E295" t="n">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="F295" t="b">
         <v>0</v>
@@ -16595,7 +16532,7 @@
         <v>45893</v>
       </c>
       <c r="E296" t="n">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="F296" t="b">
         <v>0</v>
@@ -16621,7 +16558,7 @@
         <v>45915</v>
       </c>
       <c r="E297" t="n">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="F297" t="b">
         <v>0</v>
@@ -16647,7 +16584,7 @@
         <v>45915</v>
       </c>
       <c r="E298" t="n">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="F298" t="b">
         <v>0</v>
@@ -16673,7 +16610,7 @@
         <v>45920</v>
       </c>
       <c r="E299" t="n">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F299" t="b">
         <v>0</v>
@@ -16699,7 +16636,7 @@
         <v>45920</v>
       </c>
       <c r="E300" t="n">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F300" t="b">
         <v>0</v>
@@ -16725,7 +16662,7 @@
         <v>45924</v>
       </c>
       <c r="E301" t="n">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="F301" t="b">
         <v>0</v>
@@ -16751,7 +16688,7 @@
         <v>45936</v>
       </c>
       <c r="E302" t="n">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="F302" t="b">
         <v>0</v>
@@ -16777,7 +16714,7 @@
         <v>45944</v>
       </c>
       <c r="E303" t="n">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="F303" t="b">
         <v>0</v>
@@ -16803,7 +16740,7 @@
         <v>45950</v>
       </c>
       <c r="E304" t="n">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="F304" t="b">
         <v>0</v>
@@ -16829,7 +16766,7 @@
         <v>45952</v>
       </c>
       <c r="E305" t="n">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="F305" t="b">
         <v>0</v>
@@ -16855,7 +16792,7 @@
         <v>45954</v>
       </c>
       <c r="E306" t="n">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="F306" t="b">
         <v>0</v>
@@ -16881,7 +16818,7 @@
         <v>45956</v>
       </c>
       <c r="E307" t="n">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="F307" t="b">
         <v>0</v>
@@ -16907,7 +16844,7 @@
         <v>45958</v>
       </c>
       <c r="E308" t="n">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="F308" t="b">
         <v>0</v>
@@ -16933,7 +16870,7 @@
         <v>45959</v>
       </c>
       <c r="E309" t="n">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F309" t="b">
         <v>0</v>
@@ -16959,7 +16896,7 @@
         <v>45959</v>
       </c>
       <c r="E310" t="n">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F310" t="b">
         <v>0</v>
@@ -16985,7 +16922,7 @@
         <v>45967</v>
       </c>
       <c r="E311" t="n">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="F311" t="b">
         <v>0</v>
@@ -17011,7 +16948,7 @@
         <v>45968</v>
       </c>
       <c r="E312" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="F312" t="b">
         <v>0</v>
@@ -17037,7 +16974,7 @@
         <v>45976</v>
       </c>
       <c r="E313" t="n">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="F313" t="b">
         <v>0</v>
@@ -17063,7 +17000,7 @@
         <v>45980</v>
       </c>
       <c r="E314" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F314" t="b">
         <v>0</v>
@@ -17089,7 +17026,7 @@
         <v>45981</v>
       </c>
       <c r="E315" t="n">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="F315" t="b">
         <v>0</v>
@@ -17115,7 +17052,7 @@
         <v>45986</v>
       </c>
       <c r="E316" t="n">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F316" t="b">
         <v>0</v>
@@ -17141,7 +17078,7 @@
         <v>45995</v>
       </c>
       <c r="E317" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="F317" t="b">
         <v>0</v>
@@ -17167,7 +17104,7 @@
         <v>45997</v>
       </c>
       <c r="E318" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="F318" t="b">
         <v>0</v>
@@ -17193,7 +17130,7 @@
         <v>45999</v>
       </c>
       <c r="E319" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="F319" t="b">
         <v>0</v>
@@ -17219,7 +17156,7 @@
         <v>45999</v>
       </c>
       <c r="E320" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="F320" t="b">
         <v>0</v>
@@ -17245,7 +17182,7 @@
         <v>46000</v>
       </c>
       <c r="E321" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="F321" t="b">
         <v>0</v>
@@ -17271,7 +17208,7 @@
         <v>46001</v>
       </c>
       <c r="E322" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="F322" t="b">
         <v>0</v>
@@ -17297,7 +17234,7 @@
         <v>46002</v>
       </c>
       <c r="E323" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="F323" t="b">
         <v>0</v>
@@ -17323,7 +17260,7 @@
         <v>46003</v>
       </c>
       <c r="E324" t="n">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="F324" t="b">
         <v>0</v>
@@ -17349,7 +17286,7 @@
         <v>46010</v>
       </c>
       <c r="E325" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="F325" t="b">
         <v>0</v>
@@ -17375,7 +17312,7 @@
         <v>46013</v>
       </c>
       <c r="E326" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F326" t="b">
         <v>0</v>
@@ -17401,7 +17338,7 @@
         <v>46019</v>
       </c>
       <c r="E327" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F327" t="b">
         <v>0</v>
@@ -17427,7 +17364,7 @@
         <v>46024</v>
       </c>
       <c r="E328" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="F328" t="b">
         <v>0</v>
@@ -17453,7 +17390,7 @@
         <v>46025</v>
       </c>
       <c r="E329" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F329" t="b">
         <v>0</v>
@@ -17479,7 +17416,7 @@
         <v>46028</v>
       </c>
       <c r="E330" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F330" t="b">
         <v>0</v>
@@ -17505,7 +17442,7 @@
         <v>46029</v>
       </c>
       <c r="E331" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F331" t="b">
         <v>0</v>
@@ -17531,7 +17468,7 @@
         <v>46029</v>
       </c>
       <c r="E332" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F332" t="b">
         <v>0</v>
@@ -17557,7 +17494,7 @@
         <v>46032</v>
       </c>
       <c r="E333" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F333" t="b">
         <v>0</v>
@@ -17583,7 +17520,7 @@
         <v>46035</v>
       </c>
       <c r="E334" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F334" t="b">
         <v>0</v>
@@ -17609,7 +17546,7 @@
         <v>46035</v>
       </c>
       <c r="E335" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F335" t="b">
         <v>0</v>
@@ -17635,7 +17572,7 @@
         <v>46040</v>
       </c>
       <c r="E336" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F336" t="b">
         <v>0</v>
@@ -17661,7 +17598,7 @@
         <v>46042</v>
       </c>
       <c r="E337" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="F337" t="b">
         <v>0</v>
@@ -17687,7 +17624,7 @@
         <v>46043</v>
       </c>
       <c r="E338" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F338" t="b">
         <v>0</v>
@@ -17713,7 +17650,7 @@
         <v>46044</v>
       </c>
       <c r="E339" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F339" t="b">
         <v>0</v>
@@ -17739,7 +17676,7 @@
         <v>46045</v>
       </c>
       <c r="E340" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F340" t="b">
         <v>0</v>
@@ -17765,7 +17702,7 @@
         <v>46045</v>
       </c>
       <c r="E341" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F341" t="b">
         <v>0</v>
@@ -17791,7 +17728,7 @@
         <v>46045</v>
       </c>
       <c r="E342" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F342" t="b">
         <v>0</v>
@@ -17817,7 +17754,7 @@
         <v>46051</v>
       </c>
       <c r="E343" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F343" t="b">
         <v>1</v>
@@ -17843,7 +17780,7 @@
         <v>46053</v>
       </c>
       <c r="E344" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F344" t="b">
         <v>0</v>
@@ -17869,7 +17806,7 @@
         <v>46056</v>
       </c>
       <c r="E345" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F345" t="b">
         <v>0</v>
@@ -17895,7 +17832,7 @@
         <v>46061</v>
       </c>
       <c r="E346" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F346" t="b">
         <v>0</v>
@@ -17921,7 +17858,7 @@
         <v>46061</v>
       </c>
       <c r="E347" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F347" t="b">
         <v>0</v>
@@ -17947,7 +17884,7 @@
         <v>46065</v>
       </c>
       <c r="E348" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F348" t="b">
         <v>0</v>
@@ -17973,7 +17910,7 @@
         <v>46066</v>
       </c>
       <c r="E349" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F349" t="b">
         <v>0</v>
@@ -17999,7 +17936,7 @@
         <v>46068</v>
       </c>
       <c r="E350" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F350" t="b">
         <v>0</v>
@@ -18025,7 +17962,7 @@
         <v>46070</v>
       </c>
       <c r="E351" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F351" t="b">
         <v>0</v>
@@ -18051,7 +17988,7 @@
         <v>46070</v>
       </c>
       <c r="E352" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F352" t="b">
         <v>0</v>
@@ -18077,7 +18014,7 @@
         <v>46070</v>
       </c>
       <c r="E353" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F353" t="b">
         <v>0</v>
@@ -18103,7 +18040,7 @@
         <v>46072</v>
       </c>
       <c r="E354" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F354" t="b">
         <v>1</v>
@@ -18129,7 +18066,7 @@
         <v>46078</v>
       </c>
       <c r="E355" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F355" t="b">
         <v>0</v>
@@ -18155,7 +18092,7 @@
         <v>46079</v>
       </c>
       <c r="E356" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F356" t="b">
         <v>0</v>
@@ -18181,7 +18118,7 @@
         <v>46084</v>
       </c>
       <c r="E357" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F357" t="b">
         <v>0</v>
@@ -18207,7 +18144,7 @@
         <v>46085</v>
       </c>
       <c r="E358" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F358" t="b">
         <v>0</v>
@@ -18233,7 +18170,7 @@
         <v>46115</v>
       </c>
       <c r="E359" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F359" t="b">
         <v>0</v>
@@ -18259,7 +18196,7 @@
         <v>46124</v>
       </c>
       <c r="E360" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F360" t="b">
         <v>0</v>
@@ -33285,7 +33222,7 @@
         <v>46157</v>
       </c>
       <c r="E986" t="n">
-        <v>-27</v>
+        <v>-22</v>
       </c>
       <c r="F986" t="b">
         <v>0</v>
@@ -33311,7 +33248,7 @@
         <v>46171</v>
       </c>
       <c r="E987" t="n">
-        <v>-41</v>
+        <v>-36</v>
       </c>
       <c r="F987" t="b">
         <v>0</v>
@@ -33337,7 +33274,7 @@
         <v>46171</v>
       </c>
       <c r="E988" t="n">
-        <v>-41</v>
+        <v>-36</v>
       </c>
       <c r="F988" t="b">
         <v>0</v>
@@ -33363,7 +33300,7 @@
         <v>46179</v>
       </c>
       <c r="E989" t="n">
-        <v>-49</v>
+        <v>-44</v>
       </c>
       <c r="F989" t="b">
         <v>0</v>
@@ -33389,7 +33326,7 @@
         <v>46179</v>
       </c>
       <c r="E990" t="n">
-        <v>-49</v>
+        <v>-44</v>
       </c>
       <c r="F990" t="b">
         <v>0</v>
@@ -33415,7 +33352,7 @@
         <v>46189</v>
       </c>
       <c r="E991" t="n">
-        <v>-59</v>
+        <v>-54</v>
       </c>
       <c r="F991" t="b">
         <v>0</v>
@@ -33441,7 +33378,7 @@
         <v>46194</v>
       </c>
       <c r="E992" t="n">
-        <v>-64</v>
+        <v>-59</v>
       </c>
       <c r="F992" t="b">
         <v>0</v>
@@ -33467,7 +33404,7 @@
         <v>46206</v>
       </c>
       <c r="E993" t="n">
-        <v>-76</v>
+        <v>-71</v>
       </c>
       <c r="F993" t="b">
         <v>0</v>
@@ -33493,7 +33430,7 @@
         <v>46212</v>
       </c>
       <c r="E994" t="n">
-        <v>-82</v>
+        <v>-77</v>
       </c>
       <c r="F994" t="b">
         <v>1</v>
@@ -33519,7 +33456,7 @@
         <v>46218</v>
       </c>
       <c r="E995" t="n">
-        <v>-88</v>
+        <v>-83</v>
       </c>
       <c r="F995" t="b">
         <v>0</v>
@@ -33545,7 +33482,7 @@
         <v>46225</v>
       </c>
       <c r="E996" t="n">
-        <v>-95</v>
+        <v>-90</v>
       </c>
       <c r="F996" t="b">
         <v>0</v>
@@ -33571,7 +33508,7 @@
         <v>46227</v>
       </c>
       <c r="E997" t="n">
-        <v>-97</v>
+        <v>-92</v>
       </c>
       <c r="F997" t="b">
         <v>0</v>
@@ -33597,7 +33534,7 @@
         <v>46251</v>
       </c>
       <c r="E998" t="n">
-        <v>-121</v>
+        <v>-116</v>
       </c>
       <c r="F998" t="b">
         <v>0</v>
@@ -33623,7 +33560,7 @@
         <v>46281</v>
       </c>
       <c r="E999" t="n">
-        <v>-151</v>
+        <v>-146</v>
       </c>
       <c r="F999" t="b">
         <v>0</v>
@@ -33649,7 +33586,7 @@
         <v>46286</v>
       </c>
       <c r="E1000" t="n">
-        <v>-156</v>
+        <v>-151</v>
       </c>
       <c r="F1000" t="b">
         <v>0</v>
@@ -33675,7 +33612,7 @@
         <v>46308</v>
       </c>
       <c r="E1001" t="n">
-        <v>-178</v>
+        <v>-173</v>
       </c>
       <c r="F1001" t="b">
         <v>0</v>
@@ -33701,7 +33638,7 @@
         <v>46324</v>
       </c>
       <c r="E1002" t="n">
-        <v>-194</v>
+        <v>-189</v>
       </c>
       <c r="F1002" t="b">
         <v>0</v>
